--- a/V-bending_Dataset.xlsx
+++ b/V-bending_Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/80b4f0e888d86282/2026_V-bending_Project-01/V-bending/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{6A62A133-2A56-40FC-ABEE-84ACE1E794E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D43DFC55-EADB-43FD-997C-7D6D6F94533D}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{6A62A133-2A56-40FC-ABEE-84ACE1E794E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86D4786A-B11C-4B03-85A6-72EA8871D408}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{95762EF2-8225-47DC-A8E3-FE4B7BA92C84}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95762EF2-8225-47DC-A8E3-FE4B7BA92C84}"/>
   </bookViews>
   <sheets>
     <sheet name="81 runs" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -317,9 +317,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -342,7 +342,7 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -828,6 +828,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1182,22 +1186,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F37437-1A10-4C22-9364-FA07B617DF01}">
   <dimension ref="A1:K82"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1232,7 +1236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1265,10 +1269,10 @@
         <v>81.755555556666664</v>
       </c>
       <c r="K2" s="15">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1301,10 +1305,10 @@
         <v>81.833333333333329</v>
       </c>
       <c r="K3" s="16">
-        <v>0.156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1340,7 +1344,7 @@
         <v>0.17699999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1376,7 +1380,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1409,10 +1413,10 @@
         <v>81.677777776666659</v>
       </c>
       <c r="K6" s="16">
-        <v>5.8999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1448,7 +1452,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1481,10 +1485,10 @@
         <v>81.644444446666668</v>
       </c>
       <c r="K8" s="16">
-        <v>7.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1520,7 +1524,7 @@
         <v>0.19700000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1553,10 +1557,10 @@
         <v>81.65555555666667</v>
       </c>
       <c r="K10" s="16">
-        <v>0.16200000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1589,10 +1593,10 @@
         <v>85.511111113333342</v>
       </c>
       <c r="K11" s="16">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1625,10 +1629,10 @@
         <v>84.455555556666667</v>
       </c>
       <c r="K12" s="16">
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -1661,10 +1665,10 @@
         <v>84.544444443333333</v>
       </c>
       <c r="K13" s="16">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -1697,10 +1701,10 @@
         <v>85.5</v>
       </c>
       <c r="K14" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -1733,10 +1737,10 @@
         <v>81.933333333333337</v>
       </c>
       <c r="K15" s="16">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -1769,10 +1773,10 @@
         <v>81.644444443333327</v>
       </c>
       <c r="K16" s="16">
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -1808,7 +1812,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -1841,10 +1845,10 @@
         <v>85</v>
       </c>
       <c r="K18" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -1880,7 +1884,7 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -1913,10 +1917,10 @@
         <v>93.377777776666676</v>
       </c>
       <c r="K20" s="16">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -1949,10 +1953,10 @@
         <v>92.911111109999993</v>
       </c>
       <c r="K21" s="16">
-        <v>8.4000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -1985,10 +1989,10 @@
         <v>93.32222222</v>
       </c>
       <c r="K22" s="16">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -2021,10 +2025,10 @@
         <v>93</v>
       </c>
       <c r="K23" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -2057,10 +2061,10 @@
         <v>90.566666670000004</v>
       </c>
       <c r="K24" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -2093,10 +2097,10 @@
         <v>88.033333330000005</v>
       </c>
       <c r="K25" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -2129,10 +2133,10 @@
         <v>92.877777776666662</v>
       </c>
       <c r="K26" s="16">
-        <v>0.107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -2165,10 +2169,10 @@
         <v>92.033333333333346</v>
       </c>
       <c r="K27" s="16">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -2204,7 +2208,7 @@
         <v>0.17699999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -2240,7 +2244,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -2276,7 +2280,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -2309,10 +2313,10 @@
         <v>81.733333333333334</v>
       </c>
       <c r="K31" s="16">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -2345,10 +2349,10 @@
         <v>81.52222222333333</v>
       </c>
       <c r="K32" s="16">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>32</v>
       </c>
@@ -2381,10 +2385,10 @@
         <v>81.544444443333333</v>
       </c>
       <c r="K33" s="16">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>33</v>
       </c>
@@ -2417,10 +2421,10 @@
         <v>81.666666666666671</v>
       </c>
       <c r="K34" s="16">
-        <v>0.13800000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>34</v>
       </c>
@@ -2453,10 +2457,10 @@
         <v>81.600000000000009</v>
       </c>
       <c r="K35" s="16">
-        <v>0.10299999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -2489,10 +2493,10 @@
         <v>81.533333336666672</v>
       </c>
       <c r="K36" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>36</v>
       </c>
@@ -2525,10 +2529,10 @@
         <v>81.32222222</v>
       </c>
       <c r="K37" s="16">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -2561,10 +2565,10 @@
         <v>84.922222219999995</v>
       </c>
       <c r="K38" s="16">
-        <v>9.9000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>38</v>
       </c>
@@ -2597,10 +2601,10 @@
         <v>83.744444443333336</v>
       </c>
       <c r="K39" s="16">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -2633,10 +2637,10 @@
         <v>84</v>
       </c>
       <c r="K40" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -2669,10 +2673,10 @@
         <v>85</v>
       </c>
       <c r="K41" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -2705,10 +2709,10 @@
         <v>82.011111110000002</v>
       </c>
       <c r="K42" s="16">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>42</v>
       </c>
@@ -2741,10 +2745,10 @@
         <v>85.17777778</v>
       </c>
       <c r="K43" s="16">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -2777,10 +2781,10 @@
         <v>84.377777780000002</v>
       </c>
       <c r="K44" s="16">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>44</v>
       </c>
@@ -2813,10 +2817,10 @@
         <v>82.055555556666661</v>
       </c>
       <c r="K45" s="16">
-        <v>0.16200000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -2852,7 +2856,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -2885,10 +2889,10 @@
         <v>93.688888889999987</v>
       </c>
       <c r="K47" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -2921,10 +2925,10 @@
         <v>93.333333333333329</v>
       </c>
       <c r="K48" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>48</v>
       </c>
@@ -2957,10 +2961,10 @@
         <v>93.322222223333327</v>
       </c>
       <c r="K49" s="16">
-        <v>5.8999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -2993,10 +2997,10 @@
         <v>93.399999999999991</v>
       </c>
       <c r="K50" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>50</v>
       </c>
@@ -3029,10 +3033,10 @@
         <v>90.977777779999997</v>
       </c>
       <c r="K51" s="16">
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>51</v>
       </c>
@@ -3065,10 +3069,10 @@
         <v>91.433333333333323</v>
       </c>
       <c r="K52" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>52</v>
       </c>
@@ -3104,7 +3108,7 @@
         <v>0.182</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -3137,10 +3141,10 @@
         <v>92.5</v>
       </c>
       <c r="K54" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>54</v>
       </c>
@@ -3173,10 +3177,10 @@
         <v>92.566666666666663</v>
       </c>
       <c r="K55" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>55</v>
       </c>
@@ -3209,10 +3213,10 @@
         <v>81.588888890000007</v>
       </c>
       <c r="K56" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>56</v>
       </c>
@@ -3245,10 +3249,10 @@
         <v>81.566666663333336</v>
       </c>
       <c r="K57" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -3281,10 +3285,10 @@
         <v>81.777777776666667</v>
       </c>
       <c r="K58" s="16">
-        <v>5.8999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>58</v>
       </c>
@@ -3317,10 +3321,10 @@
         <v>81.266666666666666</v>
       </c>
       <c r="K59" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -3356,7 +3360,7 @@
         <v>0.191</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>60</v>
       </c>
@@ -3389,10 +3393,10 @@
         <v>81.044444443333333</v>
       </c>
       <c r="K61" s="16">
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -3428,7 +3432,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>62</v>
       </c>
@@ -3464,7 +3468,7 @@
         <v>0.17699999999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -3497,10 +3501,10 @@
         <v>81.144444446666668</v>
       </c>
       <c r="K64" s="16">
-        <v>0.192</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>64</v>
       </c>
@@ -3533,10 +3537,10 @@
         <v>83.666666669999998</v>
       </c>
       <c r="K65" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -3569,10 +3573,10 @@
         <v>82.666666666666671</v>
       </c>
       <c r="K66" s="16">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>66</v>
       </c>
@@ -3605,10 +3609,10 @@
         <v>83.7</v>
       </c>
       <c r="K67" s="16">
-        <v>0.10299999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>67</v>
       </c>
@@ -3641,10 +3645,10 @@
         <v>83.455555556666667</v>
       </c>
       <c r="K68" s="16">
-        <v>8.6999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>68</v>
       </c>
@@ -3677,10 +3681,10 @@
         <v>81.855555556666658</v>
       </c>
       <c r="K69" s="16">
-        <v>0.188</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>69</v>
       </c>
@@ -3716,7 +3720,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>70</v>
       </c>
@@ -3749,10 +3753,10 @@
         <v>84.266666663333339</v>
       </c>
       <c r="K71" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>71</v>
       </c>
@@ -3788,7 +3792,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>72</v>
       </c>
@@ -3821,10 +3825,10 @@
         <v>82.255555556666664</v>
       </c>
       <c r="K73" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>73</v>
       </c>
@@ -3857,10 +3861,10 @@
         <v>93.366666663333334</v>
       </c>
       <c r="K74" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>74</v>
       </c>
@@ -3893,10 +3897,10 @@
         <v>93.5</v>
       </c>
       <c r="K75" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>75</v>
       </c>
@@ -3929,10 +3933,10 @@
         <v>93.90000000000002</v>
       </c>
       <c r="K76" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>76</v>
       </c>
@@ -3965,10 +3969,10 @@
         <v>93.755555556666664</v>
       </c>
       <c r="K77" s="16">
-        <v>8.6999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>77</v>
       </c>
@@ -4001,10 +4005,10 @@
         <v>90.633333336666666</v>
       </c>
       <c r="K78" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>78</v>
       </c>
@@ -4037,10 +4041,10 @@
         <v>92.833333333333329</v>
       </c>
       <c r="K79" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>79</v>
       </c>
@@ -4073,10 +4077,10 @@
         <v>93.233333329999994</v>
       </c>
       <c r="K80" s="16">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -4109,10 +4113,10 @@
         <v>92.28888889000001</v>
       </c>
       <c r="K81" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
         <v>81</v>
       </c>
@@ -4145,7 +4149,7 @@
         <v>92.333333330000002</v>
       </c>
       <c r="K82" s="17">
-        <v>1.2E-2</v>
+        <v>1.6E-2</v>
       </c>
     </row>
   </sheetData>
